--- a/data/trans_dic/IP07_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP07_R2-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,69; 6,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,48</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,99</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,63</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,66</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,75; 6,22</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,7; 6,93</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,4</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,69</t>
+          <t>0,8; 7,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,55</t>
+          <t>0,56; 3,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,51</t>
+          <t>0,68; 4,8</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,37%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,43</t>
+          <t>0,71; 6,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>0,5; 5,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 8,85</t>
+          <t>0,93; 8,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 7,16</t>
+          <t>0,72; 5,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 3,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,99</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,89</t>
+          <t>0,88; 8,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,12</t>
+          <t>1,14; 5,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,22</t>
+          <t>0,34; 3,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,99</t>
+          <t>0,31; 3,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,15</t>
+          <t>1,38; 6,46</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,42%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2,38%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>1,32; 7,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 10,2</t>
+          <t>0,0; 5,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 9,32</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,27</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,36</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0,99; 9,58</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,31; 8,03</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,12</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,76</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,16</t>
+          <t>0,81; 4,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,72</t>
+          <t>0,92; 5,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>0,0; 4,78</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,07%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,53</t>
+          <t>1,0; 4,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,51</t>
+          <t>2,31; 6,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,98</t>
+          <t>1,38; 5,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 14,52</t>
+          <t>1,17; 4,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,73</t>
+          <t>0,64; 3,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 7,24</t>
+          <t>1,45; 5,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,46</t>
+          <t>0,79; 3,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,3</t>
+          <t>0,84; 5,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,39</t>
+          <t>1,15; 3,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,51</t>
+          <t>2,19; 5,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,88</t>
+          <t>1,38; 4,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 8,48</t>
+          <t>1,4; 4,06</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,8%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,79%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,59</t>
+          <t>2,18; 8,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,49</t>
+          <t>0,77; 4,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 7,32</t>
+          <t>0,88; 4,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,71</t>
+          <t>0,91; 5,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,96</t>
+          <t>0,6; 5,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,8</t>
+          <t>1,08; 6,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,31</t>
+          <t>1,95; 7,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,63</t>
+          <t>1,12; 6,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,01</t>
+          <t>2,0; 6,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,26</t>
+          <t>1,26; 4,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,45</t>
+          <t>1,73; 5,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,78</t>
+          <t>1,35; 4,73</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5,57%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>1,76; 10,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 12,87</t>
+          <t>0,82; 7,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 5,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,93</t>
+          <t>0,82; 8,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 11,05</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,71</t>
+          <t>1,49; 13,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,42</t>
+          <t>1,29; 10,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,01</t>
+          <t>1,27; 6,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,61; 7,38</t>
+          <t>1,68; 7,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,11</t>
+          <t>0,46; 3,98</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,86</t>
+          <t>1,51; 7,35</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2,46%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2,01%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,54</t>
+          <t>2,34; 4,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,75</t>
+          <t>1,44; 3,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,1</t>
+          <t>1,33; 3,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,42</t>
+          <t>1,6; 3,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,63</t>
+          <t>0,91; 2,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,15</t>
+          <t>1,59; 3,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,25</t>
+          <t>1,29; 3,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,71</t>
+          <t>1,63; 4,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,27</t>
+          <t>1,82; 3,17</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,07</t>
+          <t>1,75; 3,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,77</t>
+          <t>1,52; 2,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,29</t>
+          <t>1,87; 3,31</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,62 +1859,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2682</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2151</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>448</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2560</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2682</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2712</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>1285</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2280</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3130</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4863</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2451</t>
+          <t>678; 6733</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4448</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0; 4445</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 7343</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2740</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5049</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>786; 6502</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>680; 6757</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4359</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 7790</t>
+          <t>828; 7347</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1132; 7165</t>
+          <t>1132; 7468</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4357</t>
+          <t>0; 3911</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4570</t>
+          <t>0; 4496</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1734; 10898</t>
+          <t>1539; 10825</t>
         </is>
       </c>
     </row>
@@ -2009,32 +2009,32 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2069</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1067</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3114</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2143</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1286</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5922</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>623; 5616</t>
+          <t>608; 5695</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4088</t>
+          <t>0; 3988</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3434</t>
+          <t>558; 6269</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1110; 8379</t>
+          <t>847; 7308</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>607; 6104</t>
+          <t>633; 5096</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4484</t>
+          <t>0; 3497</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>560; 5582</t>
+          <t>0; 3389</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>858; 7544</t>
+          <t>850; 8114</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1581; 8838</t>
+          <t>1965; 9418</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>650; 6099</t>
+          <t>650; 5768</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>669; 6471</t>
+          <t>672; 6670</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2580; 11703</t>
+          <t>2586; 12148</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,44 +2275,44 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3340</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>622</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1276</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2116</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3340</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1525</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
           <t>3962</t>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1438</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3002</t>
+          <t>1312; 7789</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3884</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>614; 6308</t>
+          <t>0; 4480</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0; 5308</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3550</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4581</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>611; 5924</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1305; 7979</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3864</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4957</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1923; 8602</t>
+          <t>1352; 7980</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4308</t>
+          <t>0; 4137</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1237; 7852</t>
+          <t>1259; 8000</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 5222</t>
+          <t>0; 5274</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4730</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9620</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6159</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3388</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6311</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4245</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9347</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4730</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9620</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6159</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>9380</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1313; 7090</t>
+          <t>2016; 9416</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2906; 11312</t>
+          <t>5243; 15426</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1659; 8867</t>
+          <t>2916; 12190</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2400; 31774</t>
+          <t>2369; 9558</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2036; 9481</t>
+          <t>1282; 7898</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5680; 16455</t>
+          <t>2986; 11763</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2716; 11505</t>
+          <t>1757; 8728</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2773; 11579</t>
+          <t>1501; 8986</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4145; 13599</t>
+          <t>4627; 13868</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10532; 23842</t>
+          <t>9489; 23197</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5768; 16848</t>
+          <t>5981; 17475</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7430; 37057</t>
+          <t>5347; 15484</t>
         </is>
       </c>
     </row>
@@ -2623,37 +2623,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5986</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3075</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3415</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3495</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>2551</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>4174</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>5156</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3370</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>5986</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3075</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3415</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>6634</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>626; 5820</t>
+          <t>2762; 10461</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1855; 8195</t>
+          <t>1073; 6738</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2374; 9974</t>
+          <t>1265; 7119</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1187; 8019</t>
+          <t>1355; 8602</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2759; 11351</t>
+          <t>627; 5892</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1277; 6699</t>
+          <t>1604; 9192</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1337; 7594</t>
+          <t>2662; 9934</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1417; 9148</t>
+          <t>1333; 7652</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5044; 13876</t>
+          <t>4625; 13978</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3893; 12298</t>
+          <t>3637; 12790</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4730; 15213</t>
+          <t>4820; 14601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3689; 13475</t>
+          <t>3595; 12634</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3901</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1908</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2153</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>587</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1206</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2753</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3901</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1908</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5033</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2942</t>
+          <t>1273; 7756</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>769; 6940</t>
+          <t>605; 5220</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3729</t>
+          <t>0; 4009</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>774; 6843</t>
+          <t>563; 5920</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1340; 8001</t>
+          <t>0; 2930</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>604; 5656</t>
+          <t>805; 7053</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3315</t>
+          <t>0; 4205</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>619; 6781</t>
+          <t>910; 7480</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1892; 8845</t>
+          <t>1872; 8905</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2045; 9386</t>
+          <t>2142; 9949</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>587; 5206</t>
+          <t>582; 5048</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1991; 9668</t>
+          <t>2091; 10188</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>22783</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>15890</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>14799</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>17131</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>9665</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>16619</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>13398</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>21144</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>22783</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>15890</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>14799</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>39813</t>
+          <t>33271</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5536; 16199</t>
+          <t>15967; 31173</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11165; 25379</t>
+          <t>10293; 23739</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8432; 20665</t>
+          <t>9383; 22293</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12878; 42284</t>
+          <t>11018; 25762</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15853; 31580</t>
+          <t>5817; 15929</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10112; 22487</t>
+          <t>10770; 25082</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9412; 23015</t>
+          <t>8585; 20776</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>11861; 27791</t>
+          <t>10132; 25634</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>24323; 43201</t>
+          <t>23970; 41900</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23642; 42608</t>
+          <t>24270; 42611</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20369; 38025</t>
+          <t>20920; 39014</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28283; 60358</t>
+          <t>24472; 43433</t>
         </is>
       </c>
     </row>
